--- a/data/raw/Svalbard/Density_cores_KF2018_NICE/N-ICE_Ice_Station_2015_02_12_with_density_100426.xlsx
+++ b/data/raw/Svalbard/Density_cores_KF2018_NICE/N-ICE_Ice_Station_2015_02_12_with_density_100426.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\evsalg001\Documents\MATLAB\Density parametrization\Svalbard\Density_cores_KF2018_NICE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\evsalg001\Documents\MATLAB\Density parametrization\script\data\raw\Svalbard\Density_cores_KF2018_NICE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5FE1ADF-0948-4E89-AB0E-064BD3BBB502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B08B849-23A3-4CC5-9C96-603D255A3266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" tabRatio="867" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="867" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Station Overview" sheetId="1" r:id="rId1"/>
@@ -1913,6 +1913,21 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -1976,21 +1991,6 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -3417,13 +3417,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="31.5" x14ac:dyDescent="0.5">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="155" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="151"/>
-      <c r="C1" s="151"/>
-      <c r="D1" s="151"/>
-      <c r="E1" s="151"/>
+      <c r="B1" s="155"/>
+      <c r="C1" s="155"/>
+      <c r="D1" s="155"/>
+      <c r="E1" s="155"/>
       <c r="F1" s="46"/>
       <c r="G1" s="46"/>
       <c r="H1" s="46"/>
@@ -3447,10 +3447,10 @@
       <c r="A4" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="154" t="s">
+      <c r="B4" s="158" t="s">
         <v>159</v>
       </c>
-      <c r="C4" s="155"/>
+      <c r="C4" s="159"/>
       <c r="H4" s="50"/>
       <c r="I4" s="50"/>
     </row>
@@ -3458,10 +3458,10 @@
       <c r="A5" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="156">
+      <c r="B5" s="160">
         <v>1</v>
       </c>
-      <c r="C5" s="157"/>
+      <c r="C5" s="161"/>
       <c r="H5" s="50"/>
       <c r="I5" s="50"/>
     </row>
@@ -3469,19 +3469,19 @@
       <c r="A6" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="156">
+      <c r="B6" s="160">
         <v>29</v>
       </c>
-      <c r="C6" s="157"/>
+      <c r="C6" s="161"/>
     </row>
     <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="B7" s="158" t="s">
+      <c r="B7" s="162" t="s">
         <v>160</v>
       </c>
-      <c r="C7" s="159"/>
+      <c r="C7" s="163"/>
     </row>
     <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="49" t="s">
@@ -3492,46 +3492,46 @@
       <c r="A10" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="152" t="s">
+      <c r="B10" s="156" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="152"/>
-      <c r="D10" s="152"/>
-      <c r="E10" s="153"/>
+      <c r="C10" s="156"/>
+      <c r="D10" s="156"/>
+      <c r="E10" s="157"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="143" t="s">
+      <c r="B11" s="147" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="143"/>
-      <c r="D11" s="143"/>
-      <c r="E11" s="144"/>
+      <c r="C11" s="147"/>
+      <c r="D11" s="147"/>
+      <c r="E11" s="148"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="147"/>
-      <c r="C12" s="147"/>
-      <c r="D12" s="147"/>
-      <c r="E12" s="148"/>
+      <c r="B12" s="151"/>
+      <c r="C12" s="151"/>
+      <c r="D12" s="151"/>
+      <c r="E12" s="152"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="20"/>
-      <c r="B13" s="147"/>
-      <c r="C13" s="147"/>
-      <c r="D13" s="147"/>
-      <c r="E13" s="148"/>
+      <c r="B13" s="151"/>
+      <c r="C13" s="151"/>
+      <c r="D13" s="151"/>
+      <c r="E13" s="152"/>
     </row>
     <row r="14" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="21"/>
-      <c r="B14" s="149"/>
-      <c r="C14" s="149"/>
-      <c r="D14" s="149"/>
-      <c r="E14" s="150"/>
+      <c r="B14" s="153"/>
+      <c r="C14" s="153"/>
+      <c r="D14" s="153"/>
+      <c r="E14" s="154"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="52"/>
@@ -3664,24 +3664,24 @@
       <c r="A30" s="45" t="s">
         <v>144</v>
       </c>
-      <c r="B30" s="145" t="s">
+      <c r="B30" s="149" t="s">
         <v>5</v>
       </c>
-      <c r="C30" s="145"/>
-      <c r="D30" s="145"/>
-      <c r="E30" s="146"/>
+      <c r="C30" s="149"/>
+      <c r="D30" s="149"/>
+      <c r="E30" s="150"/>
     </row>
     <row r="31" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="32" spans="1:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="63"/>
-      <c r="B32" s="162" t="s">
+      <c r="B32" s="143" t="s">
         <v>143</v>
       </c>
-      <c r="C32" s="162"/>
-      <c r="D32" s="162" t="s">
+      <c r="C32" s="143"/>
+      <c r="D32" s="143" t="s">
         <v>142</v>
       </c>
-      <c r="E32" s="162"/>
+      <c r="E32" s="143"/>
       <c r="F32" s="14" t="s">
         <v>14</v>
       </c>
@@ -3690,50 +3690,50 @@
       <c r="A33" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="B33" s="163"/>
-      <c r="C33" s="163"/>
-      <c r="D33" s="163"/>
-      <c r="E33" s="163"/>
+      <c r="B33" s="144"/>
+      <c r="C33" s="144"/>
+      <c r="D33" s="144"/>
+      <c r="E33" s="144"/>
       <c r="F33" s="70"/>
     </row>
     <row r="34" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="B34" s="160"/>
-      <c r="C34" s="160"/>
-      <c r="D34" s="160"/>
-      <c r="E34" s="160"/>
+      <c r="B34" s="145"/>
+      <c r="C34" s="145"/>
+      <c r="D34" s="145"/>
+      <c r="E34" s="145"/>
       <c r="F34" s="71"/>
     </row>
     <row r="35" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="B35" s="160"/>
-      <c r="C35" s="160"/>
-      <c r="D35" s="160"/>
-      <c r="E35" s="160"/>
+      <c r="B35" s="145"/>
+      <c r="C35" s="145"/>
+      <c r="D35" s="145"/>
+      <c r="E35" s="145"/>
       <c r="F35" s="71"/>
     </row>
     <row r="36" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="B36" s="160"/>
-      <c r="C36" s="160"/>
-      <c r="D36" s="160"/>
-      <c r="E36" s="160"/>
+      <c r="B36" s="145"/>
+      <c r="C36" s="145"/>
+      <c r="D36" s="145"/>
+      <c r="E36" s="145"/>
       <c r="F36" s="71"/>
     </row>
     <row r="37" spans="1:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="B37" s="161"/>
-      <c r="C37" s="161"/>
-      <c r="D37" s="161"/>
-      <c r="E37" s="161"/>
+      <c r="B37" s="146"/>
+      <c r="C37" s="146"/>
+      <c r="D37" s="146"/>
+      <c r="E37" s="146"/>
       <c r="F37" s="72"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -3801,18 +3801,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D37:E37"/>
     <mergeCell ref="B11:E11"/>
     <mergeCell ref="B30:E30"/>
     <mergeCell ref="B12:E14"/>
@@ -3822,6 +3810,18 @@
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
   </mergeCells>
   <dataValidations xWindow="316" yWindow="263" count="26">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Must be blank if entered decimal degrees in first cell; otherwise, must be a  number between 0 and 60" prompt="Ending longitude seconds (0 to less than 60)_x000a_Leave blank if decimal degrees entered in previous cell" sqref="E28" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -4365,12 +4365,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="155" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="151"/>
-      <c r="C1" s="151"/>
-      <c r="D1" s="151"/>
+      <c r="B1" s="155"/>
+      <c r="C1" s="155"/>
+      <c r="D1" s="155"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
@@ -5973,6 +5973,28 @@
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="E36:F36"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B2:C2"/>
@@ -5985,28 +6007,6 @@
     <mergeCell ref="E22:F22"/>
     <mergeCell ref="E23:F23"/>
     <mergeCell ref="E24:F24"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="E43:F43"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C7" xr:uid="{00000000-0002-0000-0400-000000000000}">
@@ -6701,7 +6701,7 @@
         <v>134</v>
       </c>
       <c r="B10" s="118">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="F10" s="124" t="s">
         <v>107</v>
